--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F60A21-4A9B-4645-A062-9E24A2C730D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80F6D9A-CEFB-41CB-9682-A5A9045DC486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2809" uniqueCount="1995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2835" uniqueCount="2019">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -5788,9 +5788,6 @@
     <t>purtroppo</t>
   </si>
   <si>
-    <t>Potresti</t>
-  </si>
-  <si>
     <t>leider</t>
   </si>
   <si>
@@ -6117,6 +6114,108 @@
   </si>
   <si>
     <t>superare</t>
+  </si>
+  <si>
+    <t>sofort, gleich</t>
+  </si>
+  <si>
+    <t>tanto</t>
+  </si>
+  <si>
+    <t>viel / sehr</t>
+  </si>
+  <si>
+    <t>tanto -&gt; m. singulari
+tanta -&gt; f. singulari
+tanti -&gt; m. pluarle
+tante -&gt; f. pluarle</t>
+  </si>
+  <si>
+    <t>invece</t>
+  </si>
+  <si>
+    <t>das Mal, die Zeit, der Anlass</t>
+  </si>
+  <si>
+    <r>
+      <t>la volta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Grazie lo stesso</t>
+  </si>
+  <si>
+    <t>Trotzdem danke / Danke trotzdem</t>
+  </si>
+  <si>
+    <t>Gern geschehen. / Keine Ursache. / Nichts zu danken.</t>
+  </si>
+  <si>
+    <t>Bitte! / Gern geschehen</t>
+  </si>
+  <si>
+    <t>Nichts zu danken.</t>
+  </si>
+  <si>
+    <t>Non c'è di che</t>
+  </si>
+  <si>
+    <t>Prego</t>
+  </si>
+  <si>
+    <t>Ach was! / Keine Ursache! (informell)</t>
+  </si>
+  <si>
+    <t>Gern geschehen! (höfliche Form)</t>
+  </si>
+  <si>
+    <t>Di niente.</t>
+  </si>
+  <si>
+    <t>Si figuri!</t>
+  </si>
+  <si>
+    <r>
+      <t>Figurati!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>Danke</t>
+  </si>
+  <si>
+    <t>Gern geschehen</t>
+  </si>
+  <si>
+    <t>Bitte / Gern geschehen. (die häufigste Antwort)</t>
+  </si>
+  <si>
+    <t>Di niente</t>
+  </si>
+  <si>
+    <t>Grazie</t>
+  </si>
+  <si>
+    <t>hingegen, stattdessen, dagegen, aber</t>
   </si>
 </sst>
 </file>
@@ -6226,7 +6325,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6248,14 +6347,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -6594,26 +6699,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>736</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7023,26 +7128,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>813</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7404,33 +7509,33 @@
   <sheetPr codeName="Tabelle12">
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="7" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7568,7 +7673,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>205</v>
       </c>
@@ -7576,7 +7681,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>213</v>
       </c>
@@ -7584,7 +7689,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1879</v>
       </c>
@@ -7592,7 +7697,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1881</v>
       </c>
@@ -7600,7 +7705,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1869</v>
       </c>
@@ -7608,17 +7713,119 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1884</v>
       </c>
       <c r="B22" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1885</v>
+        <v>229</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="22" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2015</v>
       </c>
     </row>
   </sheetData>
@@ -7627,6 +7834,7 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7639,26 +7847,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7685,55 +7893,55 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B4" t="s">
         <v>1943</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B5" t="s">
         <v>1945</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B6" t="s">
         <v>1947</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B7" t="s">
         <v>1949</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B8" t="s">
         <v>1951</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1952</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B9" t="s">
         <v>1953</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1954</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B10" t="s">
         <v>1340</v>
@@ -7741,31 +7949,31 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B11" t="s">
         <v>1956</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B12" t="s">
         <v>1958</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B13" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B14" t="s">
         <v>1360</v>
@@ -7773,15 +7981,15 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B15" t="s">
         <v>1962</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1963</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B16" t="s">
         <v>1328</v>
@@ -7789,7 +7997,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B17" t="s">
         <v>1320</v>
@@ -7797,7 +8005,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B18" t="s">
         <v>1332</v>
@@ -7805,7 +8013,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B19" t="s">
         <v>1315</v>
@@ -7813,7 +8021,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B20" t="s">
         <v>1344</v>
@@ -7821,7 +8029,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B21" t="s">
         <v>972</v>
@@ -7829,50 +8037,50 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B22" t="s">
         <v>1970</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B23" t="s">
         <v>1972</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1973</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B24" t="s">
         <v>1974</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B25" t="s">
         <v>1976</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1977</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B26" t="s">
         <v>1978</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1979</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B27" t="s">
         <v>1980</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1981</v>
       </c>
     </row>
   </sheetData>
@@ -7896,26 +8104,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7942,162 +8150,162 @@
     </row>
     <row r="4" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>1887</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="C4" s="2" t="s">
         <v>1888</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1889</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>1890</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>1891</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>1892</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>1893</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>1894</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1895</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>1896</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1897</v>
-      </c>
       <c r="C8" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>1898</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>1899</v>
-      </c>
       <c r="C9" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>1900</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>1901</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="B11" s="2" t="s">
         <v>1902</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>1903</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>1904</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>1905</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>1906</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>1907</v>
-      </c>
       <c r="C13" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>1908</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>1909</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>1910</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1911</v>
-      </c>
       <c r="C15" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>1913</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>1914</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
@@ -8105,10 +8313,10 @@
         <v>1385</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -8116,186 +8324,186 @@
         <v>1389</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>1917</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1918</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>1919</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1920</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>1921</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1922</v>
-      </c>
       <c r="C22" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>1923</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1924</v>
-      </c>
       <c r="C23" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>1925</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1926</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>1927</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1928</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>1929</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>1930</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>1932</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1934</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>1935</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1936</v>
-      </c>
       <c r="C29" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>1937</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>1938</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>1939</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>1940</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>1941</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>1942</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B33" s="13" t="s">
         <v>1982</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>1983</v>
-      </c>
       <c r="C33" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B34" t="s">
         <v>1987</v>
       </c>
-      <c r="B34" t="s">
-        <v>1988</v>
-      </c>
       <c r="C34" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B35" t="s">
         <v>1984</v>
       </c>
-      <c r="B35" t="s">
-        <v>1985</v>
-      </c>
       <c r="C35" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
@@ -8303,54 +8511,54 @@
         <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>1910</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1911</v>
-      </c>
       <c r="C39" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -8378,26 +8586,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>852</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>853</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9014,26 +9222,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>975</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9365,26 +9573,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1037</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9716,26 +9924,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1099</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10162,26 +10370,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1181</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10590,26 +10798,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11319,26 +11527,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1252</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -11670,26 +11878,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12021,26 +12229,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1375</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12277,26 +12485,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12818,26 +13026,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13169,26 +13377,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1578</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13368,26 +13576,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13586,26 +13794,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13937,26 +14145,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1670</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14231,26 +14439,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1720</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14664,34 +14872,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
@@ -15067,26 +15275,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>1780</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15621,26 +15829,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15810,26 +16018,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16219,26 +16427,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16659,26 +16867,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -17163,26 +17371,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -17799,26 +18007,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="15" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">

--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -8,50 +8,51 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96436151-E73D-4B89-BF37-17DED2FA8E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4BD58-1B6F-4A88-8D3B-5547B37BBD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
     <sheet name="Verbi Top 50" sheetId="2" r:id="rId2"/>
     <sheet name="Verbi CB" sheetId="32" r:id="rId3"/>
     <sheet name="Verbi riflessivi Top 25" sheetId="3" r:id="rId4"/>
-    <sheet name="Frequenza | Häufigkeitsadv." sheetId="4" r:id="rId5"/>
-    <sheet name="Averbi di tempo e modo" sheetId="5" r:id="rId6"/>
-    <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId7"/>
-    <sheet name="Frasi utili CB | Sätze 2" sheetId="33" r:id="rId8"/>
-    <sheet name="Meine Worte" sheetId="29" r:id="rId9"/>
-    <sheet name="Parti del corpo | Körperteile" sheetId="6" r:id="rId10"/>
-    <sheet name="Calendario | Kalender" sheetId="7" r:id="rId11"/>
-    <sheet name="Professioni | Berufe" sheetId="8" r:id="rId12"/>
-    <sheet name="Nazionalità | Nationalitäten" sheetId="9" r:id="rId13"/>
-    <sheet name="Colori | Farben" sheetId="10" r:id="rId14"/>
-    <sheet name="Wegbeschreibung" sheetId="31" r:id="rId15"/>
-    <sheet name="Traffico | Verkehr" sheetId="30" r:id="rId16"/>
-    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId17"/>
-    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId18"/>
-    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId19"/>
-    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId20"/>
-    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId21"/>
-    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId22"/>
-    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId23"/>
-    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId24"/>
-    <sheet name="Animali | Tiere" sheetId="21" r:id="rId25"/>
-    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId26"/>
-    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId27"/>
-    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId28"/>
-    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId29"/>
-    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId30"/>
-    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId31"/>
-    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId32"/>
+    <sheet name="Verbi Sätze" sheetId="34" r:id="rId5"/>
+    <sheet name="Frequenza | Häufigkeitsadv." sheetId="4" r:id="rId6"/>
+    <sheet name="Averbi di tempo e modo" sheetId="5" r:id="rId7"/>
+    <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId8"/>
+    <sheet name="Frasi utili CB | Sätze 2" sheetId="33" r:id="rId9"/>
+    <sheet name="Meine Worte" sheetId="29" r:id="rId10"/>
+    <sheet name="Parti del corpo | Körperteile" sheetId="6" r:id="rId11"/>
+    <sheet name="Calendario | Kalender" sheetId="7" r:id="rId12"/>
+    <sheet name="Professioni | Berufe" sheetId="8" r:id="rId13"/>
+    <sheet name="Nazionalità | Nationalitäten" sheetId="9" r:id="rId14"/>
+    <sheet name="Colori | Farben" sheetId="10" r:id="rId15"/>
+    <sheet name="Wegbeschreibung" sheetId="31" r:id="rId16"/>
+    <sheet name="Traffico | Verkehr" sheetId="30" r:id="rId17"/>
+    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId18"/>
+    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId19"/>
+    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId20"/>
+    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId21"/>
+    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId22"/>
+    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId23"/>
+    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId24"/>
+    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId25"/>
+    <sheet name="Animali | Tiere" sheetId="21" r:id="rId26"/>
+    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId27"/>
+    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId28"/>
+    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId29"/>
+    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId30"/>
+    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId31"/>
+    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId32"/>
+    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId33"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2901" uniqueCount="2043">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="2093">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -6488,6 +6489,156 @@
       </rPr>
       <t>deine Telefonnummer?</t>
     </r>
+  </si>
+  <si>
+    <t>Sie wissen alles.</t>
+  </si>
+  <si>
+    <t>Loro sanno tutto.</t>
+  </si>
+  <si>
+    <t>Wisst ihr, wie spät es ist?</t>
+  </si>
+  <si>
+    <t>Sapete l'ora?</t>
+  </si>
+  <si>
+    <t>Wir wissen die Wahrheit.</t>
+  </si>
+  <si>
+    <t>Sappiamo la verità.</t>
+  </si>
+  <si>
+    <t>Sie kann sehr gut kochen.</t>
+  </si>
+  <si>
+    <t>Lei sa cucinare molto bene.</t>
+  </si>
+  <si>
+    <t>Weißt du, wo er/sie wohnt?</t>
+  </si>
+  <si>
+    <t>Sai dove abita?</t>
+  </si>
+  <si>
+    <t>Ich kann schwimmen.</t>
+  </si>
+  <si>
+    <t>So nuotare.</t>
+  </si>
+  <si>
+    <t>Sie können zur Party kommen.</t>
+  </si>
+  <si>
+    <t>Loro possono venire alla festa.</t>
+  </si>
+  <si>
+    <t>Könnt ihr eine Minute warten?</t>
+  </si>
+  <si>
+    <t>Potete aspettare un minuto?</t>
+  </si>
+  <si>
+    <t>Wir können jetzt losfahren.</t>
+  </si>
+  <si>
+    <t>Possiamo partire adesso.</t>
+  </si>
+  <si>
+    <t>Er kann drei Sprachen sprechen.</t>
+  </si>
+  <si>
+    <t>Lui può parlare tre lingue.</t>
+  </si>
+  <si>
+    <t>Kannst du morgen kommen?</t>
+  </si>
+  <si>
+    <t>Puoi venire domani?</t>
+  </si>
+  <si>
+    <t>Kann ich dir helfen?</t>
+  </si>
+  <si>
+    <t>Posso aiutarti?</t>
+  </si>
+  <si>
+    <t>Sie haben ein großes Haus.</t>
+  </si>
+  <si>
+    <t>Loro hanno una casa grande.</t>
+  </si>
+  <si>
+    <t>Ihr habt recht.</t>
+  </si>
+  <si>
+    <t>Avete ragione.</t>
+  </si>
+  <si>
+    <t>Wir haben Zeit.</t>
+  </si>
+  <si>
+    <t>Abbiamo tempo.</t>
+  </si>
+  <si>
+    <t>Sie hat zwei Kinder.</t>
+  </si>
+  <si>
+    <t>Lei ha due figli.</t>
+  </si>
+  <si>
+    <t>Hast du einen Bruder?</t>
+  </si>
+  <si>
+    <t>Hai un fratello?</t>
+  </si>
+  <si>
+    <t>Ich habe Hunger.</t>
+  </si>
+  <si>
+    <t>Ho fame.</t>
+  </si>
+  <si>
+    <t>Sie sind Freunde.</t>
+  </si>
+  <si>
+    <t>Loro sono amici.</t>
+  </si>
+  <si>
+    <t>Ihr seid zu spät.</t>
+  </si>
+  <si>
+    <t>Voi siete in ritardo.</t>
+  </si>
+  <si>
+    <t>Wir sind bereit.</t>
+  </si>
+  <si>
+    <t>Noi siamo pronti.</t>
+  </si>
+  <si>
+    <t>Sie ist eine gute Lehrerin.</t>
+  </si>
+  <si>
+    <t>Lei è una brava insegnante.</t>
+  </si>
+  <si>
+    <t>Du bist sehr freundlich.</t>
+  </si>
+  <si>
+    <t>Tu sei molto gentile.</t>
+  </si>
+  <si>
+    <t>Ich bin heute müde.</t>
+  </si>
+  <si>
+    <t>Sono stanco oggi.</t>
+  </si>
+  <si>
+    <t>Je ein Satz pro Konjugation (io/tu/lui-lei/noi/voi/loro) fuer die vier wichtigsten unregelmaessigen Verben. kat = Verb, zum Filtern in der App.</t>
+  </si>
+  <si>
+    <t>Vocabolario – Sätze mit essere, avere, potere, sapere</t>
   </si>
 </sst>
 </file>
@@ -6966,6 +7117,340 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B66C6F-8A66-46FF-A81A-50D89DD6569D}">
+  <sheetPr codeName="Tabelle12">
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="19.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1870</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>257</v>
+      </c>
+      <c r="B14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1:G25"/>
@@ -7406,7 +7891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1:G26"/>
@@ -7909,7 +8394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Tabelle8"/>
   <dimension ref="A1:G33"/>
@@ -8546,7 +9031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Tabelle9"/>
   <dimension ref="A1:G46"/>
@@ -9240,7 +9725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Tabelle10"/>
   <dimension ref="A1:G22"/>
@@ -9667,7 +10152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E588DC5B-33F8-491D-A40A-9A11B571492D}">
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9922,7 +10407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0357D6F-E5C9-4C7A-8B99-03AFE50AD46D}">
   <sheetPr codeName="Tabelle29"/>
   <dimension ref="A1:G41"/>
@@ -10403,7 +10888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr codeName="Tabelle13"/>
   <dimension ref="A1:G33"/>
@@ -11039,7 +11524,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Tabelle14"/>
   <dimension ref="A1:G18"/>
@@ -11376,357 +11861,6 @@
       </c>
       <c r="E18" t="s">
         <v>1036</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <sheetPr codeName="Tabelle15"/>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1048</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1049</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1060</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1062</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1064</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1088</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1040</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1098</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -12472,6 +12606,357 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr codeName="Tabelle15"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Tabelle16"/>
   <dimension ref="A1:G23"/>
@@ -12917,7 +13402,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Tabelle17"/>
   <dimension ref="A1:G26"/>
@@ -13344,7 +13829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr codeName="Tabelle18"/>
   <dimension ref="A1:G18"/>
@@ -13695,7 +14180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr codeName="Tabelle19"/>
   <dimension ref="A1:G18"/>
@@ -14046,7 +14531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr codeName="Tabelle20"/>
   <dimension ref="A1:G13"/>
@@ -14302,7 +14787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr codeName="Tabelle21"/>
   <dimension ref="A1:G28"/>
@@ -14843,7 +15328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr codeName="Tabelle22"/>
   <dimension ref="A1:G18"/>
@@ -15194,7 +15679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr codeName="Tabelle23"/>
   <dimension ref="A1:G10"/>
@@ -15393,7 +15878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr codeName="Tabelle24"/>
   <dimension ref="A1:G11"/>
@@ -15600,357 +16085,6 @@
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <sheetPr codeName="Tabelle25"/>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>1608</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1609</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1610</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1614</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1615</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1616</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1617</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1620</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1621</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1622</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1623</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1624</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1625</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1626</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1627</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1628</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1629</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1630</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1632</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1633</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1634</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1639</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1640</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1641</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1642</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1644</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1645</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1647</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1648</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1649</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1650</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1651</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1652</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1653</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1654</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1656</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1657</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1658</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1660</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1661</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1662</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1664</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1665</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1666</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1667</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1668</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1669</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16081,6 +16215,357 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <sheetPr codeName="Tabelle25"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1617</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1624</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1628</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1644</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1645</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1648</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1649</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1656</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1657</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1664</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1668</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1669</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr codeName="Tabelle26"/>
   <dimension ref="A1:G15"/>
@@ -16374,7 +16859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr codeName="Tabelle27"/>
   <dimension ref="A1:G31"/>
@@ -16804,7 +17289,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
   <sheetPr codeName="Tabelle28"/>
   <dimension ref="A1:G42"/>
@@ -17761,6 +18246,373 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FBCF60-9B6E-4989-B8C9-F8F53A3AC6FF}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:G15"/>
@@ -17951,7 +18803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1:G21"/>
@@ -18361,7 +19213,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr codeName="Tabelle11">
     <tabColor rgb="FFFFFF00"/>
@@ -18751,7 +19603,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479EAFFB-A862-4A3D-A74F-4F6456ADFBD7}">
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
@@ -19054,338 +19906,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B66C6F-8A66-46FF-A81A-50D89DD6569D}">
-  <sheetPr codeName="Tabelle12">
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:G35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="7" width="19.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>1870</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1871</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1865</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1224</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1872</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>1867</v>
-      </c>
-      <c r="B10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1873</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>1869</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>249</v>
-      </c>
-      <c r="B13" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>1875</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>1881</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>1869</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" s="16" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="16" t="s">
-        <v>1995</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>1996</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>1998</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>2000</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>2001</v>
-      </c>
-      <c r="B27" t="s">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B28" t="s">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>2006</v>
-      </c>
-      <c r="B30" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>2012</v>
-      </c>
-      <c r="B31" t="s">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>2011</v>
-      </c>
-      <c r="B32" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>2017</v>
-      </c>
-      <c r="B33" t="s">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B34" t="s">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>2007</v>
-      </c>
-      <c r="B35" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/vocabolario_V2.4_CB.xlsx
+++ b/vocabolario_V2.4_CB.xlsx
@@ -1,58 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\01_Vokabel_App\04_Wörterbücher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E4BD58-1B6F-4A88-8D3B-5547B37BBD0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4526E2F6-789D-4AA6-BE68-2FB8EC0510F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="868" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
     <sheet name="Verbi Top 50" sheetId="2" r:id="rId2"/>
     <sheet name="Verbi CB" sheetId="32" r:id="rId3"/>
     <sheet name="Verbi riflessivi Top 25" sheetId="3" r:id="rId4"/>
-    <sheet name="Verbi Sätze" sheetId="34" r:id="rId5"/>
-    <sheet name="Frequenza | Häufigkeitsadv." sheetId="4" r:id="rId6"/>
-    <sheet name="Averbi di tempo e modo" sheetId="5" r:id="rId7"/>
-    <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId8"/>
-    <sheet name="Frasi utili CB | Sätze 2" sheetId="33" r:id="rId9"/>
-    <sheet name="Meine Worte" sheetId="29" r:id="rId10"/>
-    <sheet name="Parti del corpo | Körperteile" sheetId="6" r:id="rId11"/>
-    <sheet name="Calendario | Kalender" sheetId="7" r:id="rId12"/>
-    <sheet name="Professioni | Berufe" sheetId="8" r:id="rId13"/>
-    <sheet name="Nazionalità | Nationalitäten" sheetId="9" r:id="rId14"/>
-    <sheet name="Colori | Farben" sheetId="10" r:id="rId15"/>
-    <sheet name="Wegbeschreibung" sheetId="31" r:id="rId16"/>
-    <sheet name="Traffico | Verkehr" sheetId="30" r:id="rId17"/>
-    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId18"/>
-    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId19"/>
-    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId20"/>
-    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId21"/>
-    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId22"/>
-    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId23"/>
-    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId24"/>
-    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId25"/>
-    <sheet name="Animali | Tiere" sheetId="21" r:id="rId26"/>
-    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId27"/>
-    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId28"/>
-    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId29"/>
-    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId30"/>
-    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId31"/>
-    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId32"/>
-    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId33"/>
+    <sheet name="Gemüse" sheetId="36" r:id="rId5"/>
+    <sheet name="Obst" sheetId="35" r:id="rId6"/>
+    <sheet name="Verbi Sätze" sheetId="34" r:id="rId7"/>
+    <sheet name="Frequenza | Häufigkeitsadv." sheetId="4" r:id="rId8"/>
+    <sheet name="Averbi di tempo e modo" sheetId="5" r:id="rId9"/>
+    <sheet name="Frasi utili CB | Sätze " sheetId="12" r:id="rId10"/>
+    <sheet name="Frasi utili CB | Sätze 2" sheetId="33" r:id="rId11"/>
+    <sheet name="Meine Worte" sheetId="29" r:id="rId12"/>
+    <sheet name="Parti del corpo | Körperteile" sheetId="6" r:id="rId13"/>
+    <sheet name="Calendario | Kalender" sheetId="7" r:id="rId14"/>
+    <sheet name="Professioni | Berufe" sheetId="8" r:id="rId15"/>
+    <sheet name="Nazionalità | Nationalitäten" sheetId="9" r:id="rId16"/>
+    <sheet name="Colori | Farben" sheetId="10" r:id="rId17"/>
+    <sheet name="Wegbeschreibung" sheetId="31" r:id="rId18"/>
+    <sheet name="Traffico | Verkehr" sheetId="30" r:id="rId19"/>
+    <sheet name="Gli hobby | Hobbys" sheetId="13" r:id="rId20"/>
+    <sheet name="l'abbigliamento | Kleidung" sheetId="14" r:id="rId21"/>
+    <sheet name="Famiglia | Familie" sheetId="15" r:id="rId22"/>
+    <sheet name="Cibo e bevande | Essen&amp;Trinken" sheetId="16" r:id="rId23"/>
+    <sheet name="L'orario | Uhrzeit" sheetId="17" r:id="rId24"/>
+    <sheet name="Casa e mobili | Zuhause &amp; Möbel" sheetId="18" r:id="rId25"/>
+    <sheet name="Città e luoghi | Stadt &amp; Orte" sheetId="19" r:id="rId26"/>
+    <sheet name="Mezzi transp. | Verkehrsmittel" sheetId="20" r:id="rId27"/>
+    <sheet name="Animali | Tiere" sheetId="21" r:id="rId28"/>
+    <sheet name="Salute | Gesundheit" sheetId="22" r:id="rId29"/>
+    <sheet name="Interrogativi | Fragewörter" sheetId="23" r:id="rId30"/>
+    <sheet name="Preposizioni | Präpositionen" sheetId="24" r:id="rId31"/>
+    <sheet name="Tratti caratt. | Charaktereig." sheetId="25" r:id="rId32"/>
+    <sheet name="Emozioni | Gefühle" sheetId="26" r:id="rId33"/>
+    <sheet name="Numeri 1-100 | Zahlen 1-100" sheetId="27" r:id="rId34"/>
+    <sheet name="numeri ordinali | Ordungszahlen" sheetId="28" r:id="rId35"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2980" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3144" uniqueCount="2216">
   <si>
     <t>Vocabolario – Präpositionen</t>
   </si>
@@ -6639,6 +6641,375 @@
   </si>
   <si>
     <t>Vocabolario – Sätze mit essere, avere, potere, sapere</t>
+  </si>
+  <si>
+    <t>Die Mandarine lässt sich leicht schälen.</t>
+  </si>
+  <si>
+    <t>Il mandarino è facile da sbucciare.</t>
+  </si>
+  <si>
+    <t>Obst</t>
+  </si>
+  <si>
+    <t>die Mandarine</t>
+  </si>
+  <si>
+    <t>il mandarino</t>
+  </si>
+  <si>
+    <t>Die Aprikose ist klein und süß.</t>
+  </si>
+  <si>
+    <t>L'albicocca è piccola e dolce.</t>
+  </si>
+  <si>
+    <t>die Aprikose</t>
+  </si>
+  <si>
+    <t>l'albicocca</t>
+  </si>
+  <si>
+    <t>Die Kiwi ist innen grün.</t>
+  </si>
+  <si>
+    <t>Il kiwi è verde dentro.</t>
+  </si>
+  <si>
+    <t>die Kiwi</t>
+  </si>
+  <si>
+    <t>il kiwi</t>
+  </si>
+  <si>
+    <t>Kirschen wachsen auf dem Baum.</t>
+  </si>
+  <si>
+    <t>Le ciliegie crescono sull'albero.</t>
+  </si>
+  <si>
+    <t>die Kirsche</t>
+  </si>
+  <si>
+    <t>la ciliegia</t>
+  </si>
+  <si>
+    <t>Die Wassermelone ist voller Wasser.</t>
+  </si>
+  <si>
+    <t>L'anguria è piena d'acqua.</t>
+  </si>
+  <si>
+    <t>die Wassermelone</t>
+  </si>
+  <si>
+    <t>l'anguria</t>
+  </si>
+  <si>
+    <t>Die Melone ist im Sommer erfrischend.</t>
+  </si>
+  <si>
+    <t>Il melone è fresco d'estate.</t>
+  </si>
+  <si>
+    <t>die Melone</t>
+  </si>
+  <si>
+    <t>il melone</t>
+  </si>
+  <si>
+    <t>Die Ananas ist eine tropische Frucht.</t>
+  </si>
+  <si>
+    <t>L'ananas è un frutto tropicale.</t>
+  </si>
+  <si>
+    <t>die Ananas</t>
+  </si>
+  <si>
+    <t>l'ananas</t>
+  </si>
+  <si>
+    <t>Der Pfirsich hat eine weiche Schale.</t>
+  </si>
+  <si>
+    <t>La pesca ha la buccia morbida.</t>
+  </si>
+  <si>
+    <t>der Pfirsich</t>
+  </si>
+  <si>
+    <t>Die Birne ist reif.</t>
+  </si>
+  <si>
+    <t>La pera è matura.</t>
+  </si>
+  <si>
+    <t>die Birne</t>
+  </si>
+  <si>
+    <t>la pera</t>
+  </si>
+  <si>
+    <t>Trauben werden zur Weinherstellung verwendet.</t>
+  </si>
+  <si>
+    <t>L'uva si usa per fare il vino.</t>
+  </si>
+  <si>
+    <t>die Traube</t>
+  </si>
+  <si>
+    <t>l'uva</t>
+  </si>
+  <si>
+    <t>Erdbeeren sind im Sommer süß.</t>
+  </si>
+  <si>
+    <t>Le fragole sono dolci in estate.</t>
+  </si>
+  <si>
+    <t>die Erdbeere</t>
+  </si>
+  <si>
+    <t>la fragola</t>
+  </si>
+  <si>
+    <t>Ich gebe Zitrone in den Tee.</t>
+  </si>
+  <si>
+    <t>Metto il limone nel tè.</t>
+  </si>
+  <si>
+    <t>die Zitrone</t>
+  </si>
+  <si>
+    <t>il limone</t>
+  </si>
+  <si>
+    <t>Ich presse eine Orange zum Frühstück aus.</t>
+  </si>
+  <si>
+    <t>Spremo un'arancia per la colazione.</t>
+  </si>
+  <si>
+    <t>die Orange</t>
+  </si>
+  <si>
+    <t>l'arancia</t>
+  </si>
+  <si>
+    <t>Die Banane ist reich an Kalium.</t>
+  </si>
+  <si>
+    <t>La banana è ricca di potassio.</t>
+  </si>
+  <si>
+    <t>die Banane</t>
+  </si>
+  <si>
+    <t>la banana</t>
+  </si>
+  <si>
+    <t>Ich esse jeden Tag einen Apfel.</t>
+  </si>
+  <si>
+    <t>Mangio una mela ogni giorno.</t>
+  </si>
+  <si>
+    <t>der Apfel</t>
+  </si>
+  <si>
+    <t>la mela</t>
+  </si>
+  <si>
+    <t>Vocabolario – Obst</t>
+  </si>
+  <si>
+    <t>Der Pilz wächst im Wald.</t>
+  </si>
+  <si>
+    <t>Il fungo cresce nel bosco.</t>
+  </si>
+  <si>
+    <t>Gemüse</t>
+  </si>
+  <si>
+    <t>der Pilz</t>
+  </si>
+  <si>
+    <t>il fungo</t>
+  </si>
+  <si>
+    <t>Sellerie hat einen starken Geschmack.</t>
+  </si>
+  <si>
+    <t>Il sedano ha un sapore forte.</t>
+  </si>
+  <si>
+    <t>der Sellerie</t>
+  </si>
+  <si>
+    <t>il sedano</t>
+  </si>
+  <si>
+    <t>Die Gurke ist frisch und knackig.</t>
+  </si>
+  <si>
+    <t>Il cetriolo è fresco e croccante.</t>
+  </si>
+  <si>
+    <t>die Gurke</t>
+  </si>
+  <si>
+    <t>il cetriolo</t>
+  </si>
+  <si>
+    <t>Ich mache Salat zum Abendessen.</t>
+  </si>
+  <si>
+    <t>Preparo l'insalata per cena.</t>
+  </si>
+  <si>
+    <t>der Salat</t>
+  </si>
+  <si>
+    <t>l'insalata</t>
+  </si>
+  <si>
+    <t>Brokkoli ist grün und gesund.</t>
+  </si>
+  <si>
+    <t>Il broccolo è verde e sano.</t>
+  </si>
+  <si>
+    <t>der Brokkoli</t>
+  </si>
+  <si>
+    <t>il broccolo</t>
+  </si>
+  <si>
+    <t>Kohl wird für Sauerkraut verwendet.</t>
+  </si>
+  <si>
+    <t>Il cavolo si usa per i crauti.</t>
+  </si>
+  <si>
+    <t>der Kohl</t>
+  </si>
+  <si>
+    <t>il cavolo</t>
+  </si>
+  <si>
+    <t>Spinat ist reich an Eisen.</t>
+  </si>
+  <si>
+    <t>Gli spinaci sono ricchi di ferro.</t>
+  </si>
+  <si>
+    <t>der Spinat</t>
+  </si>
+  <si>
+    <t>gli spinaci</t>
+  </si>
+  <si>
+    <t>Die rote Paprika ist süß.</t>
+  </si>
+  <si>
+    <t>Il peperone rosso è dolce.</t>
+  </si>
+  <si>
+    <t>die Paprika</t>
+  </si>
+  <si>
+    <t>il peperone</t>
+  </si>
+  <si>
+    <t>Die Aubergine ist dunkelviolett.</t>
+  </si>
+  <si>
+    <t>La melanzana è viola scuro.</t>
+  </si>
+  <si>
+    <t>die Aubergine</t>
+  </si>
+  <si>
+    <t>la melanzana</t>
+  </si>
+  <si>
+    <t>Ich grille die Zucchini.</t>
+  </si>
+  <si>
+    <t>Cucino la zucchina alla griglia.</t>
+  </si>
+  <si>
+    <t>die Zucchini</t>
+  </si>
+  <si>
+    <t>la zucchina</t>
+  </si>
+  <si>
+    <t>Knoblauch verleiht dem Gericht Geschmack.</t>
+  </si>
+  <si>
+    <t>L'aglio dà sapore al piatto.</t>
+  </si>
+  <si>
+    <t>der Knoblauch</t>
+  </si>
+  <si>
+    <t>l'aglio</t>
+  </si>
+  <si>
+    <t>Ich schneide die Zwiebel für die Soße.</t>
+  </si>
+  <si>
+    <t>Taglio la cipolla per il sugo.</t>
+  </si>
+  <si>
+    <t>die Zwiebel</t>
+  </si>
+  <si>
+    <t>la cipolla</t>
+  </si>
+  <si>
+    <t>Die Tomate ist rot und reif.</t>
+  </si>
+  <si>
+    <t>Il pomodoro è rosso e maturo.</t>
+  </si>
+  <si>
+    <t>die Tomate</t>
+  </si>
+  <si>
+    <t>il pomodoro</t>
+  </si>
+  <si>
+    <t>Ich mache Ofenkartoffeln.</t>
+  </si>
+  <si>
+    <t>Faccio le patate al forno.</t>
+  </si>
+  <si>
+    <t>die Kartoffel</t>
+  </si>
+  <si>
+    <t>la patata</t>
+  </si>
+  <si>
+    <t>Das Kaninchen isst die Karotte.</t>
+  </si>
+  <si>
+    <t>Il coniglio mangia la carota.</t>
+  </si>
+  <si>
+    <t>die Karotte</t>
+  </si>
+  <si>
+    <t>la carota</t>
+  </si>
+  <si>
+    <t>Vocabolario – Gemüse</t>
   </si>
 </sst>
 </file>
@@ -6785,8 +7156,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -7117,6 +7488,701 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr codeName="Tabelle11">
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:G40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="5" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>846</v>
+      </c>
+      <c r="B21" t="s">
+        <v>847</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>848</v>
+      </c>
+      <c r="B22" t="s">
+        <v>849</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C39" s="2"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C40" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479EAFFB-A862-4A3D-A74F-4F6456ADFBD7}">
+  <sheetPr>
+    <tabColor rgb="FFFFFF00"/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="5" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>814</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C32" s="2"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C33" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B66C6F-8A66-46FF-A81A-50D89DD6569D}">
   <sheetPr codeName="Tabelle12">
     <tabColor rgb="FFFFFF00"/>
@@ -7131,23 +8197,23 @@
       <c r="A1" s="17" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7450,7 +8516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="A1:G25"/>
@@ -7466,23 +8532,23 @@
       <c r="A1" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -7891,7 +8957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Tabelle7"/>
   <dimension ref="A1:G26"/>
@@ -7906,23 +8972,23 @@
       <c r="A1" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>386</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -8394,7 +9460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Tabelle8"/>
   <dimension ref="A1:G33"/>
@@ -8410,23 +9476,23 @@
       <c r="A1" s="17" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9031,7 +10097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Tabelle9"/>
   <dimension ref="A1:G46"/>
@@ -9046,23 +10112,23 @@
       <c r="A1" s="17" t="s">
         <v>572</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -9725,7 +10791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr codeName="Tabelle10"/>
   <dimension ref="A1:G22"/>
@@ -9740,23 +10806,23 @@
       <c r="A1" s="17" t="s">
         <v>735</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>736</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10152,7 +11218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E588DC5B-33F8-491D-A40A-9A11B571492D}">
   <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10164,23 +11230,23 @@
       <c r="A1" s="17" t="s">
         <v>1862</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10407,7 +11473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0357D6F-E5C9-4C7A-8B99-03AFE50AD46D}">
   <sheetPr codeName="Tabelle29"/>
   <dimension ref="A1:G41"/>
@@ -10429,15 +11495,15 @@
       <c r="G1" s="17"/>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>814</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -10884,993 +11950,6 @@
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <sheetPr codeName="Tabelle13"/>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>852</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>853</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>855</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D4" t="s">
-        <v>857</v>
-      </c>
-      <c r="E4" t="s">
-        <v>858</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>859</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D5" t="s">
-        <v>861</v>
-      </c>
-      <c r="E5" t="s">
-        <v>862</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D6" t="s">
-        <v>865</v>
-      </c>
-      <c r="E6" t="s">
-        <v>866</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>867</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>868</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D7" t="s">
-        <v>869</v>
-      </c>
-      <c r="E7" t="s">
-        <v>870</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>871</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>872</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D8" t="s">
-        <v>873</v>
-      </c>
-      <c r="E8" t="s">
-        <v>874</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D9" t="s">
-        <v>877</v>
-      </c>
-      <c r="E9" t="s">
-        <v>878</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>880</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D10" t="s">
-        <v>881</v>
-      </c>
-      <c r="E10" t="s">
-        <v>882</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D11" t="s">
-        <v>885</v>
-      </c>
-      <c r="E11" t="s">
-        <v>886</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>888</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D12" t="s">
-        <v>889</v>
-      </c>
-      <c r="E12" t="s">
-        <v>890</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D13" t="s">
-        <v>893</v>
-      </c>
-      <c r="E13" t="s">
-        <v>894</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D14" t="s">
-        <v>897</v>
-      </c>
-      <c r="E14" t="s">
-        <v>898</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D15" t="s">
-        <v>901</v>
-      </c>
-      <c r="E15" t="s">
-        <v>902</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>903</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>904</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D16" t="s">
-        <v>905</v>
-      </c>
-      <c r="E16" t="s">
-        <v>906</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D17" t="s">
-        <v>909</v>
-      </c>
-      <c r="E17" t="s">
-        <v>910</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D18" t="s">
-        <v>913</v>
-      </c>
-      <c r="E18" t="s">
-        <v>914</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>916</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D19" t="s">
-        <v>917</v>
-      </c>
-      <c r="E19" t="s">
-        <v>918</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>919</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>920</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D20" t="s">
-        <v>921</v>
-      </c>
-      <c r="E20" t="s">
-        <v>922</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>923</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>924</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D21" t="s">
-        <v>925</v>
-      </c>
-      <c r="E21" t="s">
-        <v>926</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>928</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D22" t="s">
-        <v>929</v>
-      </c>
-      <c r="E22" t="s">
-        <v>930</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>931</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>932</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D23" t="s">
-        <v>933</v>
-      </c>
-      <c r="E23" t="s">
-        <v>934</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D24" t="s">
-        <v>937</v>
-      </c>
-      <c r="E24" t="s">
-        <v>938</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D25" t="s">
-        <v>941</v>
-      </c>
-      <c r="E25" t="s">
-        <v>942</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D26" t="s">
-        <v>945</v>
-      </c>
-      <c r="E26" t="s">
-        <v>946</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D27" t="s">
-        <v>949</v>
-      </c>
-      <c r="E27" t="s">
-        <v>950</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>951</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>952</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D28" t="s">
-        <v>953</v>
-      </c>
-      <c r="E28" t="s">
-        <v>954</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>955</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>956</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D29" t="s">
-        <v>957</v>
-      </c>
-      <c r="E29" t="s">
-        <v>958</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D30" t="s">
-        <v>961</v>
-      </c>
-      <c r="E30" t="s">
-        <v>962</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>964</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D31" t="s">
-        <v>965</v>
-      </c>
-      <c r="E31" t="s">
-        <v>966</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D32" t="s">
-        <v>969</v>
-      </c>
-      <c r="E32" t="s">
-        <v>970</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>972</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>856</v>
-      </c>
-      <c r="D33" t="s">
-        <v>973</v>
-      </c>
-      <c r="E33" t="s">
-        <v>974</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <sheetPr codeName="Tabelle14"/>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>975</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>977</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D4" t="s">
-        <v>979</v>
-      </c>
-      <c r="E4" t="s">
-        <v>980</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>981</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D5" t="s">
-        <v>983</v>
-      </c>
-      <c r="E5" t="s">
-        <v>984</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>985</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D6" t="s">
-        <v>987</v>
-      </c>
-      <c r="E6" t="s">
-        <v>988</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>990</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D7" t="s">
-        <v>991</v>
-      </c>
-      <c r="E7" t="s">
-        <v>992</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D8" t="s">
-        <v>995</v>
-      </c>
-      <c r="E8" t="s">
-        <v>996</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D9" t="s">
-        <v>999</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E11" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1015</v>
-      </c>
-      <c r="E13" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1019</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E16" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1034</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>978</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1035</v>
-      </c>
-      <c r="E18" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
@@ -11891,23 +11970,23 @@
       <c r="A1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12606,6 +12685,993 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr codeName="Tabelle13"/>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>853</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>854</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D4" t="s">
+        <v>857</v>
+      </c>
+      <c r="E4" t="s">
+        <v>858</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D5" t="s">
+        <v>861</v>
+      </c>
+      <c r="E5" t="s">
+        <v>862</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>863</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D6" t="s">
+        <v>865</v>
+      </c>
+      <c r="E6" t="s">
+        <v>866</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D7" t="s">
+        <v>869</v>
+      </c>
+      <c r="E7" t="s">
+        <v>870</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D8" t="s">
+        <v>873</v>
+      </c>
+      <c r="E8" t="s">
+        <v>874</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D9" t="s">
+        <v>877</v>
+      </c>
+      <c r="E9" t="s">
+        <v>878</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D10" t="s">
+        <v>881</v>
+      </c>
+      <c r="E10" t="s">
+        <v>882</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>884</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D11" t="s">
+        <v>885</v>
+      </c>
+      <c r="E11" t="s">
+        <v>886</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D12" t="s">
+        <v>889</v>
+      </c>
+      <c r="E12" t="s">
+        <v>890</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D13" t="s">
+        <v>893</v>
+      </c>
+      <c r="E13" t="s">
+        <v>894</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D14" t="s">
+        <v>897</v>
+      </c>
+      <c r="E14" t="s">
+        <v>898</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D15" t="s">
+        <v>901</v>
+      </c>
+      <c r="E15" t="s">
+        <v>902</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D16" t="s">
+        <v>905</v>
+      </c>
+      <c r="E16" t="s">
+        <v>906</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D17" t="s">
+        <v>909</v>
+      </c>
+      <c r="E17" t="s">
+        <v>910</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D18" t="s">
+        <v>913</v>
+      </c>
+      <c r="E18" t="s">
+        <v>914</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D19" t="s">
+        <v>917</v>
+      </c>
+      <c r="E19" t="s">
+        <v>918</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D20" t="s">
+        <v>921</v>
+      </c>
+      <c r="E20" t="s">
+        <v>922</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D21" t="s">
+        <v>925</v>
+      </c>
+      <c r="E21" t="s">
+        <v>926</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D22" t="s">
+        <v>929</v>
+      </c>
+      <c r="E22" t="s">
+        <v>930</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>931</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D23" t="s">
+        <v>933</v>
+      </c>
+      <c r="E23" t="s">
+        <v>934</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D24" t="s">
+        <v>937</v>
+      </c>
+      <c r="E24" t="s">
+        <v>938</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D25" t="s">
+        <v>941</v>
+      </c>
+      <c r="E25" t="s">
+        <v>942</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D26" t="s">
+        <v>945</v>
+      </c>
+      <c r="E26" t="s">
+        <v>946</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D27" t="s">
+        <v>949</v>
+      </c>
+      <c r="E27" t="s">
+        <v>950</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D28" t="s">
+        <v>953</v>
+      </c>
+      <c r="E28" t="s">
+        <v>954</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D29" t="s">
+        <v>957</v>
+      </c>
+      <c r="E29" t="s">
+        <v>958</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D30" t="s">
+        <v>961</v>
+      </c>
+      <c r="E30" t="s">
+        <v>962</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D31" t="s">
+        <v>965</v>
+      </c>
+      <c r="E31" t="s">
+        <v>966</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D32" t="s">
+        <v>969</v>
+      </c>
+      <c r="E32" t="s">
+        <v>970</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="D33" t="s">
+        <v>973</v>
+      </c>
+      <c r="E33" t="s">
+        <v>974</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr codeName="Tabelle14"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D4" t="s">
+        <v>979</v>
+      </c>
+      <c r="E4" t="s">
+        <v>980</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D5" t="s">
+        <v>983</v>
+      </c>
+      <c r="E5" t="s">
+        <v>984</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E6" t="s">
+        <v>988</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D7" t="s">
+        <v>991</v>
+      </c>
+      <c r="E7" t="s">
+        <v>992</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D8" t="s">
+        <v>995</v>
+      </c>
+      <c r="E8" t="s">
+        <v>996</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D9" t="s">
+        <v>999</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr codeName="Tabelle15"/>
   <dimension ref="A1:G18"/>
@@ -12620,23 +13686,23 @@
       <c r="A1" s="17" t="s">
         <v>1037</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -12956,7 +14022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr codeName="Tabelle16"/>
   <dimension ref="A1:G23"/>
@@ -12971,23 +14037,23 @@
       <c r="A1" s="17" t="s">
         <v>1099</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13402,7 +14468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr codeName="Tabelle17"/>
   <dimension ref="A1:G26"/>
@@ -13417,23 +14483,23 @@
       <c r="A1" s="17" t="s">
         <v>1181</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -13829,7 +14895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr codeName="Tabelle18"/>
   <dimension ref="A1:G18"/>
@@ -13844,23 +14910,23 @@
       <c r="A1" s="17" t="s">
         <v>1252</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14180,7 +15246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr codeName="Tabelle19"/>
   <dimension ref="A1:G18"/>
@@ -14195,23 +15261,23 @@
       <c r="A1" s="17" t="s">
         <v>1313</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14531,7 +15597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr codeName="Tabelle20"/>
   <dimension ref="A1:G13"/>
@@ -14546,23 +15612,23 @@
       <c r="A1" s="17" t="s">
         <v>1375</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -14787,7 +15853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr codeName="Tabelle21"/>
   <dimension ref="A1:G28"/>
@@ -14802,23 +15868,23 @@
       <c r="A1" s="17" t="s">
         <v>1417</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15328,7 +16394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr codeName="Tabelle22"/>
   <dimension ref="A1:G18"/>
@@ -15343,23 +16409,23 @@
       <c r="A1" s="17" t="s">
         <v>1517</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -15668,423 +16734,6 @@
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <sheetPr codeName="Tabelle23"/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>1578</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>1579</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1580</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1582</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1583</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>1588</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1590</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1591</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>1592</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1593</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1594</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1595</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>1596</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>1597</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1598</v>
-      </c>
-      <c r="E8" t="s">
-        <v>1599</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>1600</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>1601</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1602</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1603</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>1604</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1605</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>1581</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1606</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1607</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <sheetPr codeName="Tabelle24"/>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="42" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -16111,23 +16760,23 @@
       <c r="A1" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16215,6 +16864,423 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <sheetPr codeName="Tabelle23"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1587</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1598</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1599</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1603</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <sheetPr codeName="Tabelle24"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="42" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr codeName="Tabelle25"/>
   <dimension ref="A1:G18"/>
@@ -16229,23 +17295,23 @@
       <c r="A1" s="17" t="s">
         <v>1608</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16565,7 +17631,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr codeName="Tabelle26"/>
   <dimension ref="A1:G15"/>
@@ -16580,23 +17646,23 @@
       <c r="A1" s="17" t="s">
         <v>1670</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -16859,7 +17925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr codeName="Tabelle27"/>
   <dimension ref="A1:G31"/>
@@ -16874,23 +17940,23 @@
       <c r="A1" s="17" t="s">
         <v>1720</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -17289,7 +18355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B2A407-DA0E-4EDA-8E40-A5659FD1B0D5}">
   <sheetPr codeName="Tabelle28"/>
   <dimension ref="A1:G42"/>
@@ -17304,23 +18370,23 @@
       <c r="A1" s="17" t="s">
         <v>1780</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -18246,6 +19312,626 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84709DE6-B80A-4D15-A0F4-D1740BE5EB6D}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BF4AF35-E981-44FA-B1B9-02E6505D702F}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00FBCF60-9B6E-4989-B8C9-F8F53A3AC6FF}">
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -18265,13 +19951,13 @@
       <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>2091</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -18612,7 +20298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Tabelle4"/>
   <dimension ref="A1:G15"/>
@@ -18631,23 +20317,23 @@
       <c r="A1" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -18803,7 +20489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Tabelle5"/>
   <dimension ref="A1:G21"/>
@@ -18820,23 +20506,23 @@
       <c r="A1" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -19211,699 +20897,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <sheetPr codeName="Tabelle11">
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:G40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>813</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>850</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>1860</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>851</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>846</v>
-      </c>
-      <c r="B21" t="s">
-        <v>847</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>848</v>
-      </c>
-      <c r="B22" t="s">
-        <v>849</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C40" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479EAFFB-A862-4A3D-A74F-4F6456ADFBD7}">
-  <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
-  </sheetPr>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>813</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>814</v>
-      </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>2020</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2021</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2023</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>2024</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2025</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>2027</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>2031</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>2033</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>2034</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>2035</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>2036</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>2037</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>848</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>2038</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>2039</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>2040</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>2041</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>2042</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C33" s="2"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>